--- a/screening.xlsx
+++ b/screening.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nickt\Desktop\BP\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5514E5-8027-4502-9EA3-CFBAB4423B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{699EC2DF-E3A4-43D2-B532-03F483E55F3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{46882AD6-4D6C-438C-89B3-2ECD8C280E20}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="2" xr2:uid="{46882AD6-4D6C-438C-89B3-2ECD8C280E20}"/>
   </bookViews>
   <sheets>
     <sheet name="2004" sheetId="1" r:id="rId1"/>
@@ -86,9 +86,6 @@
     <t>N/A*</t>
   </si>
   <si>
-    <t>Phillip Morris</t>
-  </si>
-  <si>
     <t>Tržní cena</t>
   </si>
   <si>
@@ -114,6 +111,9 @@
   </si>
   <si>
     <t>COLZCZ</t>
+  </si>
+  <si>
+    <t>Philip Morris</t>
   </si>
 </sst>
 </file>
@@ -845,10 +845,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -868,7 +868,7 @@
         <v>145.69999999999999</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -888,7 +888,7 @@
         <v>289.7</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -908,7 +908,7 @@
         <v>3233</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -928,12 +928,12 @@
         <v>2440</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <v>9.86</v>
@@ -948,12 +948,12 @@
         <v>15720</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -996,10 +996,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -1019,7 +1019,7 @@
         <v>680</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -1039,7 +1039,7 @@
         <v>333</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -1059,7 +1059,7 @@
         <v>696</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -1079,12 +1079,12 @@
         <v>4130</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>13.63</v>
@@ -1099,12 +1099,12 @@
         <v>1035</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <v>8.57</v>
@@ -1119,7 +1119,7 @@
         <v>491</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1162,10 +1162,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -1185,7 +1185,7 @@
         <v>525</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -1205,7 +1205,7 @@
         <v>295</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -1225,7 +1225,7 @@
         <v>696</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -1245,12 +1245,12 @@
         <v>4440</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>22.9</v>
@@ -1265,12 +1265,12 @@
         <v>988</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <v>143.86000000000001</v>
@@ -1285,12 +1285,12 @@
         <v>593</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1333,10 +1333,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -1356,7 +1356,7 @@
         <v>591.6</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -1376,7 +1376,7 @@
         <v>235.1</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -1396,7 +1396,7 @@
         <v>549.79999999999995</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -1416,12 +1416,12 @@
         <v>4845</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>15.31</v>
@@ -1436,12 +1436,12 @@
         <v>1043</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <v>7.91</v>
@@ -1456,12 +1456,12 @@
         <v>644.5</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1504,10 +1504,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -1527,7 +1527,7 @@
         <v>430.1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -1547,7 +1547,7 @@
         <v>251.5</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -1567,7 +1567,7 @@
         <v>758.7</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -1587,12 +1587,12 @@
         <v>4880</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -1607,12 +1607,12 @@
         <v>670</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <v>9.9700000000000006</v>
@@ -1627,12 +1627,12 @@
         <v>738.4</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1675,10 +1675,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -1698,7 +1698,7 @@
         <v>422.6</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -1718,7 +1718,7 @@
         <v>264.89999999999998</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -1738,7 +1738,7 @@
         <v>764.1</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -1758,12 +1758,12 @@
         <v>887.1</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>9.98</v>
@@ -1778,12 +1778,12 @@
         <v>582.29999999999995</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <v>17.63</v>
@@ -1798,7 +1798,7 @@
         <v>766.9</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
@@ -1818,7 +1818,7 @@
         <v>82.7</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
@@ -1838,7 +1838,7 @@
         <v>490</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1881,10 +1881,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -1904,7 +1904,7 @@
         <v>509.5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -1924,7 +1924,7 @@
         <v>279</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -1944,7 +1944,7 @@
         <v>917.4</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -1964,12 +1964,12 @@
         <v>925</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>50.84</v>
@@ -1984,12 +1984,12 @@
         <v>676.5</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <v>33.090000000000003</v>
@@ -2004,7 +2004,7 @@
         <v>810</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
@@ -2024,7 +2024,7 @@
         <v>83.1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
@@ -2044,7 +2044,7 @@
         <v>362</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -2087,10 +2087,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -2110,7 +2110,7 @@
         <v>540</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -2130,7 +2130,7 @@
         <v>243.5</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -2150,7 +2150,7 @@
         <v>736.8</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -2170,12 +2170,12 @@
         <v>855</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>27.24</v>
@@ -2190,7 +2190,7 @@
         <v>516.5</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
@@ -2210,7 +2210,7 @@
         <v>72.5</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
@@ -2230,7 +2230,7 @@
         <v>420</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -2273,10 +2273,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -2296,7 +2296,7 @@
         <v>515</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -2316,7 +2316,7 @@
         <v>234</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -2336,7 +2336,7 @@
         <v>861</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -2356,12 +2356,12 @@
         <v>826</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>24.34</v>
@@ -2376,7 +2376,7 @@
         <v>638</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
@@ -2396,7 +2396,7 @@
         <v>84.65</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
@@ -2416,7 +2416,7 @@
         <v>285</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -2459,10 +2459,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -2482,7 +2482,7 @@
         <v>512</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -2502,7 +2502,7 @@
         <v>249</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -2522,7 +2522,7 @@
         <v>660</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -2542,12 +2542,12 @@
         <v>658</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>11.67</v>
@@ -2562,7 +2562,7 @@
         <v>552</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
@@ -2582,7 +2582,7 @@
         <v>69.7</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
@@ -2602,12 +2602,12 @@
         <v>283</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9">
         <v>14.19</v>
@@ -2622,7 +2622,7 @@
         <v>298</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -2665,10 +2665,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -2688,7 +2688,7 @@
         <v>806.5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -2708,7 +2708,7 @@
         <v>1026</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -2728,12 +2728,12 @@
         <v>935</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>8.5</v>
@@ -2748,7 +2748,7 @@
         <v>620</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
@@ -2768,7 +2768,7 @@
         <v>93.9</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
@@ -2788,12 +2788,12 @@
         <v>236</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>22</v>
@@ -2808,7 +2808,7 @@
         <v>506</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -2851,10 +2851,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -2874,7 +2874,7 @@
         <v>340.7</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -2894,7 +2894,7 @@
         <v>377.7</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -2914,7 +2914,7 @@
         <v>1203</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -2934,12 +2934,12 @@
         <v>3329</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <v>12.29</v>
@@ -2954,7 +2954,7 @@
         <v>16734</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2997,10 +2997,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -3020,7 +3020,7 @@
         <v>785.5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -3040,7 +3040,7 @@
         <v>723.2</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -3060,12 +3060,12 @@
         <v>659.5</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>6.13</v>
@@ -3080,7 +3080,7 @@
         <v>538</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
@@ -3100,7 +3100,7 @@
         <v>94.1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
@@ -3120,12 +3120,12 @@
         <v>310</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>9.42</v>
@@ -3140,7 +3140,7 @@
         <v>565</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -3183,10 +3183,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -3206,7 +3206,7 @@
         <v>971.5</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -3226,7 +3226,7 @@
         <v>906</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -3246,12 +3246,12 @@
         <v>725.5</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>6.16</v>
@@ -3266,7 +3266,7 @@
         <v>655</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
@@ -3286,7 +3286,7 @@
         <v>75.3</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
@@ -3306,12 +3306,12 @@
         <v>250</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>9.24</v>
@@ -3326,7 +3326,7 @@
         <v>536</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -3369,10 +3369,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -3392,7 +3392,7 @@
         <v>742.8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -3412,7 +3412,7 @@
         <v>527</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -3432,7 +3432,7 @@
         <v>1399</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -3452,12 +3452,12 @@
         <v>3456</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <v>18.309999999999999</v>
@@ -3472,7 +3472,7 @@
         <v>18241</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -3515,10 +3515,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -3538,7 +3538,7 @@
         <v>991</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -3558,7 +3558,7 @@
         <v>479.7</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -3578,7 +3578,7 @@
         <v>1638</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -3598,12 +3598,12 @@
         <v>3119</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <v>16.75</v>
@@ -3618,7 +3618,7 @@
         <v>10871</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -3662,10 +3662,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -3685,7 +3685,7 @@
         <v>1373</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -3705,7 +3705,7 @@
         <v>549</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -3725,7 +3725,7 @@
         <v>1283</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -3745,12 +3745,12 @@
         <v>4354</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <v>11.12</v>
@@ -3765,7 +3765,7 @@
         <v>7976</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -3808,10 +3808,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -3831,7 +3831,7 @@
         <v>804</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -3851,7 +3851,7 @@
         <v>425</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -3871,7 +3871,7 @@
         <v>421</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -3891,12 +3891,12 @@
         <v>3054</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <v>9.93</v>
@@ -3911,12 +3911,12 @@
         <v>6114</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7">
         <v>7.24</v>
@@ -3931,12 +3931,12 @@
         <v>645</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8">
         <v>5.51</v>
@@ -3951,7 +3951,7 @@
         <v>238</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -3994,10 +3994,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -4017,7 +4017,7 @@
         <v>864</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -4037,7 +4037,7 @@
         <v>429</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -4057,7 +4057,7 @@
         <v>696.5</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -4077,12 +4077,12 @@
         <v>3915</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <v>9.51</v>
@@ -4097,12 +4097,12 @@
         <v>8681</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7">
         <v>15.19</v>
@@ -4117,12 +4117,12 @@
         <v>959</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8">
         <v>7.44</v>
@@ -4137,7 +4137,7 @@
         <v>440</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -4180,10 +4180,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -4203,7 +4203,7 @@
         <v>783</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -4223,7 +4223,7 @@
         <v>386.5</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -4243,7 +4243,7 @@
         <v>898.4</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -4263,12 +4263,12 @@
         <v>4439</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <v>11.59</v>
@@ -4283,12 +4283,12 @@
         <v>10084</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7">
         <v>14.96</v>
@@ -4303,12 +4303,12 @@
         <v>994.6</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8">
         <v>8.27</v>
@@ -4323,7 +4323,7 @@
         <v>473</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -4366,10 +4366,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -4389,7 +4389,7 @@
         <v>791</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
@@ -4409,7 +4409,7 @@
         <v>382.5</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -4429,7 +4429,7 @@
         <v>359</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -4449,12 +4449,12 @@
         <v>3385</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <v>13.56</v>
@@ -4469,12 +4469,12 @@
         <v>12558</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7">
         <v>11.13</v>
@@ -4489,12 +4489,12 @@
         <v>815</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8">
         <v>11.86</v>
@@ -4509,7 +4509,7 @@
         <v>457</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
